--- a/Document/데이터/LUNA_System.xlsx
+++ b/Document/데이터/LUNA_System.xlsx
@@ -24,7 +24,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'ShelfItems'!$A$1:$L$41</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Personalities'!$A$1:$F$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'RandomWaves'!$A$1:$G$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Config'!$A$1:$D$32</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Config'!$A$1:$D$34</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'GradeCuts'!$A$1:$B$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'GradePayout'!$A$1:$B$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'GuestBodies'!$A$1:$J$15</definedName>
@@ -7160,13 +7160,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D32"/>
+  <dimension ref="A1:D34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
     <col width="21" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="43" customWidth="1" min="4" max="4"/>
+    <col width="54" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7825,8 +7825,48 @@
         </is>
       </c>
     </row>
+    <row r="33">
+      <c r="A33" s="7" t="inlineStr">
+        <is>
+          <t>street_typing_interval_ms</t>
+        </is>
+      </c>
+      <c r="B33" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="C33" s="7" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="D33" s="8" t="inlineStr">
+        <is>
+          <t>거리 말풍선 타이핑 문자당 간격(ms) — 바(typing_interval_ms)와 별도 튜닝</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>street_auto_next_delay_sec</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>3</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="D34" s="6" t="inlineStr">
+        <is>
+          <t>auto 재생 대사 — 타이핑 종료 후 다음 대사까지 텀</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D32"/>
+  <autoFilter ref="A1:D34"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>

--- a/Document/데이터/LUNA_System.xlsx
+++ b/Document/데이터/LUNA_System.xlsx
@@ -22,9 +22,9 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Cocktails'!$A$1:$V$18</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'RecipeLines'!$A$1:$F$42</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'ShelfItems'!$A$1:$L$41</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Personalities'!$A$1:$F$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Personalities'!$A$1:$G$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'RandomWaves'!$A$1:$G$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Config'!$A$1:$D$34</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Config'!$A$1:$D$35</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'GradeCuts'!$A$1:$B$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'GradePayout'!$A$1:$B$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'GuestBodies'!$A$1:$J$15</definedName>
@@ -529,6 +529,12 @@
       </text>
     </comment>
     <comment ref="F1" authorId="0" shapeId="0">
+      <text>
+        <t>코스터 드롭 후 order_think를 재생할 확률(0~1). 1.0=항상 고민, 0.3=대부분 즉답(ask_order 다음 바로 order). 카메오는 무관하게 항상 재생
+💡 헤더에 마우스를 올리면 이 설명이 보입니다.</t>
+      </text>
+    </comment>
+    <comment ref="G1" authorId="0" shapeId="0">
       <text>
         <t>작업 메모
 💡 헤더에 마우스를 올리면 이 설명이 보입니다.</t>
@@ -6711,7 +6717,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -6719,7 +6725,8 @@
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="34" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="46" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6750,6 +6757,11 @@
       </c>
       <c r="F1" s="4" t="inlineStr">
         <is>
+          <t>think_chance</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
           <t>note</t>
         </is>
       </c>
@@ -6776,7 +6788,10 @@
       <c r="E2" t="n">
         <v>1.2</v>
       </c>
-      <c r="F2" s="6" t="inlineStr">
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" s="6" t="inlineStr">
         <is>
           <t>예의 바르고 참을성 많음. 부정 반응도 조심스러움</t>
         </is>
@@ -6804,9 +6819,12 @@
       <c r="E3" s="7" t="n">
         <v>0.8</v>
       </c>
-      <c r="F3" s="8" t="inlineStr">
-        <is>
-          <t>입이 거침. 빨리 안 오면 폭발, 맛있으면 화끈하게 리액션</t>
+      <c r="F3" s="7" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G3" s="8" t="inlineStr">
+        <is>
+          <t>입이 거침. 빨리 안 오면 폭발, 맛있으면 화끈하게 리액션. 주문도 대부분 즉답</t>
         </is>
       </c>
     </row>
@@ -6832,7 +6850,10 @@
       <c r="E4" t="n">
         <v>0.9</v>
       </c>
-      <c r="F4" s="6" t="inlineStr">
+      <c r="F4" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
         <is>
           <t>(구)짜증난&amp;예민한 손님. 응대 하나하나에 민감</t>
         </is>
@@ -6860,7 +6881,10 @@
       <c r="E5" s="7" t="n">
         <v>1.1</v>
       </c>
-      <c r="F5" s="8" t="inlineStr">
+      <c r="F5" s="7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G5" s="8" t="inlineStr">
         <is>
           <t>말수 최소. '...'가 대사의 절반</t>
         </is>
@@ -6888,14 +6912,17 @@
       <c r="E6" t="n">
         <v>1</v>
       </c>
-      <c r="F6" s="6" t="inlineStr">
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" s="6" t="inlineStr">
         <is>
           <t>혼잣말·너스레 많음. 대사가 김</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F6"/>
+  <autoFilter ref="A1:G6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
@@ -7160,13 +7187,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D34"/>
+  <dimension ref="A1:D35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
     <col width="21" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="54" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7828,45 +7855,65 @@
     <row r="33">
       <c r="A33" s="7" t="inlineStr">
         <is>
-          <t>street_typing_interval_ms</t>
+          <t>order_bark_gap_sec</t>
         </is>
       </c>
       <c r="B33" s="7" t="n">
-        <v>50</v>
+        <v>1.5</v>
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>float</t>
         </is>
       </c>
       <c r="D33" s="8" t="inlineStr">
         <is>
-          <t>거리 말풍선 타이핑 문자당 간격(ms) — 바(typing_interval_ms)와 별도 튜닝</t>
+          <t>주문 대사 사이의 텀 — ask_order→order_think→order 순서로 재생할 때, 앞 대사 타이핑이 끝나고 다음 대사까지 기다리는 초 [가안]</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
+          <t>street_typing_interval_ms</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>50</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="D34" s="6" t="inlineStr">
+        <is>
+          <t>거리 말풍선 타이핑 문자당 간격(ms) — 바(typing_interval_ms)와 별도 튜닝</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="7" t="inlineStr">
+        <is>
           <t>street_auto_next_delay_sec</t>
         </is>
       </c>
-      <c r="B34" t="n">
+      <c r="B35" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C35" s="7" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="D34" s="6" t="inlineStr">
+      <c r="D35" s="8" t="inlineStr">
         <is>
           <t>auto 재생 대사 — 타이핑 종료 후 다음 대사까지 텀</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D34"/>
+  <autoFilter ref="A1:D35"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>

--- a/Document/데이터/LUNA_System.xlsx
+++ b/Document/데이터/LUNA_System.xlsx
@@ -9,25 +9,27 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="INFO" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cocktails" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RecipeLines" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ShelfItems" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Personalities" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RandomWaves" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Config" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GradeCuts" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GradePayout" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GuestBodies" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tags" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RecipeLines" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ShelfItems" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Personalities" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RandomWaves" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Config" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GradeCuts" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GradePayout" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GuestBodies" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Cocktails'!$A$1:$V$18</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'RecipeLines'!$A$1:$F$42</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'ShelfItems'!$A$1:$L$41</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Personalities'!$A$1:$G$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'RandomWaves'!$A$1:$G$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Config'!$A$1:$D$35</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'GradeCuts'!$A$1:$B$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'GradePayout'!$A$1:$B$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'GuestBodies'!$A$1:$J$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Cocktails'!$A$1:$Z$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Tags'!$A$1:$C$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'RecipeLines'!$A$1:$F$42</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'ShelfItems'!$A$1:$L$41</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Personalities'!$A$1:$G$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'RandomWaves'!$A$1:$G$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Config'!$A$1:$D$36</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'GradeCuts'!$A$1:$B$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'GradePayout'!$A$1:$B$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'GuestBodies'!$A$1:$J$15</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -313,17 +315,13 @@
     </comment>
     <comment ref="R1" authorId="0" shapeId="0">
       <text>
-        <t>[자동 계산 컬럼]
-빌드가 값을 채우는 칸이다. 손으로 고쳐도 다음 빌드에서 덮어써진다.
-계산 근거를 바꾸고 싶으면 재료·레시피·override 컬럼을 수정할 것.
+        <t>제조법 설명(한국어) — 정보 화면과 레시피 팝업에 그대로 뜨는 문장. 손으로 적는다. RecipeLines는 채점 정답표이고 이 칸은 표시 전용이라, 수치를 고치면 이 문장도 같이 고쳐야 한다
 💡 헤더에 마우스를 올리면 이 설명이 보입니다.</t>
       </text>
     </comment>
     <comment ref="S1" authorId="0" shapeId="0">
       <text>
-        <t>[자동 계산 컬럼]
-빌드가 값을 채우는 칸이다. 손으로 고쳐도 다음 빌드에서 덮어써진다.
-계산 근거를 바꾸고 싶으면 재료·레시피·override 컬럼을 수정할 것.
+        <t>제조법 설명(영어)
 💡 헤더에 마우스를 올리면 이 설명이 보입니다.</t>
       </text>
     </comment>
@@ -351,11 +349,147 @@
 💡 헤더에 마우스를 올리면 이 설명이 보입니다.</t>
       </text>
     </comment>
+    <comment ref="W1" authorId="0" shapeId="0">
+      <text>
+        <t>[자동 계산 컬럼]
+빌드가 값을 채우는 칸이다. 손으로 고쳐도 다음 빌드에서 덮어써진다.
+계산 근거를 바꾸고 싶으면 재료·레시피·override 컬럼을 수정할 것.
+💡 헤더에 마우스를 올리면 이 설명이 보입니다.</t>
+      </text>
+    </comment>
+    <comment ref="X1" authorId="0" shapeId="0">
+      <text>
+        <t>[자동 계산 컬럼]
+빌드가 값을 채우는 칸이다. 손으로 고쳐도 다음 빌드에서 덮어써진다.
+계산 근거를 바꾸고 싶으면 재료·레시피·override 컬럼을 수정할 것.
+💡 헤더에 마우스를 올리면 이 설명이 보입니다.</t>
+      </text>
+    </comment>
+    <comment ref="Y1" authorId="0" shapeId="0">
+      <text>
+        <t>[자동 계산 컬럼]
+빌드가 값을 채우는 칸이다. 손으로 고쳐도 다음 빌드에서 덮어써진다.
+계산 근거를 바꾸고 싶으면 재료·레시피·override 컬럼을 수정할 것.
+💡 헤더에 마우스를 올리면 이 설명이 보입니다.</t>
+      </text>
+    </comment>
+    <comment ref="Z1" authorId="0" shapeId="0">
+      <text>
+        <t>[자동 계산 컬럼]
+빌드가 값을 채우는 칸이다. 손으로 고쳐도 다음 빌드에서 덮어써진다.
+계산 근거를 바꾸고 싶으면 재료·레시피·override 컬럼을 수정할 것.
+💡 헤더에 마우스를 올리면 이 설명이 보입니다.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment10.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>LUNA 데이터 가이드</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0" shapeId="0">
+      <text>
+        <t>📋 [GuestBodies 시트]
+랜덤 손님 공용 외형 카탈로그 — 바디(얼굴·코·입 포함)×의상×눈×헤어를 성별 맞춰 조합. 스폰 시 성별 추첨 후, 그 손님 성격을 허용하는 항목만 남겨 파트별 weight 가중 랜덤
+── 이 컬럼 ──
+파트 종류 — body(바디: 얼굴·몸통·코·입·패널 라인 한 장)/outfit(의상)/eyes(눈)/hair(헤어). 스폰 시 파트별로 하나씩 추첨해 겹쳐 그린다(바디→의상→눈→헤어 순)
+💡 헤더에 마우스를 올리면 이 설명이 보입니다.</t>
+      </text>
+    </comment>
+    <comment ref="B1" authorId="0" shapeId="0">
+      <text>
+        <t>snake_case 고유 id
+💡 헤더에 마우스를 올리면 이 설명이 보입니다.</t>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="0" shapeId="0">
+      <text>
+        <t>m/f — 같은 성별 파트끼리만 조합된다
+💡 헤더에 마우스를 올리면 이 설명이 보입니다.</t>
+      </text>
+    </comment>
+    <comment ref="D1" authorId="0" shapeId="0">
+      <text>
+        <t>이 파트를 쓸 수 있는 성격 — 세미콜론 구분(예: rough;touchy). 비우면 전 성격 공용. 성격별 전용 외형을 만들 때 채운다
+💡 헤더에 마우스를 올리면 이 설명이 보입니다.</t>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="0" shapeId="0">
+      <text>
+        <t>sprite=이미지 한 장(현행) / parts_anim=파츠 애니(추후 전환용 — 단골 표정과 같은 규칙)
+💡 헤더에 마우스를 올리면 이 설명이 보입니다.</t>
+      </text>
+    </comment>
+    <comment ref="F1" authorId="0" shapeId="0">
+      <text>
+        <t>sprite 모드의 리소스 키. 아트 제작 중이라 지금은 가칭 — 완성 시 실키로 교체
+💡 헤더에 마우스를 올리면 이 설명이 보입니다.</t>
+      </text>
+    </comment>
+    <comment ref="G1" authorId="0" shapeId="0">
+      <text>
+        <t>표정별 교체 스프라이트 — '표정:키; 표정:키' (예: joy:Guest/eyes_m_1_joy; anger:…). 표정이 정해지면 이 맵에 있는 표정만 교체, 없으면 기본 sprite 유지. 비우면 표정 고정(현행). 표정은 common 세트, default 등록 금지. 감정 눈 아트가 나오면 eyes 행에 채운다
+💡 헤더에 마우스를 올리면 이 설명이 보입니다.</t>
+      </text>
+    </comment>
+    <comment ref="H1" authorId="0" shapeId="0">
+      <text>
+        <t>추첨 가중치(1 이상 정수). 클수록 자주 나온다
+💡 헤더에 마우스를 올리면 이 설명이 보입니다.</t>
+      </text>
+    </comment>
+    <comment ref="I1" authorId="0" shapeId="0">
+      <text>
+        <t>제작중/OK — 에셋 검수용, 게임 미사용
+💡 헤더에 마우스를 올리면 이 설명이 보입니다.</t>
+      </text>
+    </comment>
+    <comment ref="J1" authorId="0" shapeId="0">
+      <text>
+        <t>기획 메모 (게임 미사용)
+💡 헤더에 마우스를 올리면 이 설명이 보입니다.</t>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/comments/comment2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>LUNA 데이터 가이드</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0" shapeId="0">
+      <text>
+        <t>📋 [Tags 시트]
+맛 키워드 사전. 칵테일 tags와 Tastes의 cocktail.tag(...)이 여기 적힌 한글 태그만 쓸 수 있고, 영어 표기는 정보 화면 키워드 표시에 쓰인다
+── 이 컬럼 ──
+태그 한글 표기(정본 키). Cocktails.tags와 Tastes의 cocktail.tag(...)이 이 값을 그대로 쓴다
+💡 헤더에 마우스를 올리면 이 설명이 보입니다.</t>
+      </text>
+    </comment>
+    <comment ref="B1" authorId="0" shapeId="0">
+      <text>
+        <t>영어 표기 — 정보 화면 키워드가 EN 빌드에서 이 값을 표시
+💡 헤더에 마우스를 올리면 이 설명이 보입니다.</t>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="0" shapeId="0">
+      <text>
+        <t>작업 메모
+💡 헤더에 마우스를 올리면 이 설명이 보입니다.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment3.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>LUNA 데이터 가이드</author>
@@ -404,7 +538,7 @@
 </comments>
 </file>
 
-<file path=xl/comments/comment3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/comments/comment4.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>LUNA 데이터 가이드</author>
@@ -489,7 +623,7 @@
 </comments>
 </file>
 
-<file path=xl/comments/comment4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/comments/comment5.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>LUNA 데이터 가이드</author>
@@ -544,7 +678,7 @@
 </comments>
 </file>
 
-<file path=xl/comments/comment5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/comments/comment6.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>LUNA 데이터 가이드</author>
@@ -599,7 +733,7 @@
 </comments>
 </file>
 
-<file path=xl/comments/comment6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/comments/comment7.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>LUNA 데이터 가이드</author>
@@ -636,7 +770,7 @@
 </comments>
 </file>
 
-<file path=xl/comments/comment7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/comments/comment8.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>LUNA 데이터 가이드</author>
@@ -661,7 +795,7 @@
 </comments>
 </file>
 
-<file path=xl/comments/comment8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/comments/comment9.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>LUNA 데이터 가이드</author>
@@ -679,79 +813,6 @@
     <comment ref="B1" authorId="0" shapeId="0">
       <text>
         <t>술값 배율. 1.0=정가 다 받음, **음수면 배상**(-1.0 = 술값만큼 물어줌). sewage와 오제조만 음수
-💡 헤더에 마우스를 올리면 이 설명이 보입니다.</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
-<file path=xl/comments/comment9.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>LUNA 데이터 가이드</author>
-  </authors>
-  <commentList>
-    <comment ref="A1" authorId="0" shapeId="0">
-      <text>
-        <t>📋 [GuestBodies 시트]
-랜덤 손님 공용 외형 카탈로그 — 바디(얼굴·코·입 포함)×의상×눈×헤어를 성별 맞춰 조합. 스폰 시 성별 추첨 후, 그 손님 성격을 허용하는 항목만 남겨 파트별 weight 가중 랜덤
-── 이 컬럼 ──
-파트 종류 — body(바디: 얼굴·몸통·코·입·패널 라인 한 장)/outfit(의상)/eyes(눈)/hair(헤어). 스폰 시 파트별로 하나씩 추첨해 겹쳐 그린다(바디→의상→눈→헤어 순)
-💡 헤더에 마우스를 올리면 이 설명이 보입니다.</t>
-      </text>
-    </comment>
-    <comment ref="B1" authorId="0" shapeId="0">
-      <text>
-        <t>snake_case 고유 id
-💡 헤더에 마우스를 올리면 이 설명이 보입니다.</t>
-      </text>
-    </comment>
-    <comment ref="C1" authorId="0" shapeId="0">
-      <text>
-        <t>m/f — 같은 성별 파트끼리만 조합된다
-💡 헤더에 마우스를 올리면 이 설명이 보입니다.</t>
-      </text>
-    </comment>
-    <comment ref="D1" authorId="0" shapeId="0">
-      <text>
-        <t>이 파트를 쓸 수 있는 성격 — 세미콜론 구분(예: rough;touchy). 비우면 전 성격 공용. 성격별 전용 외형을 만들 때 채운다
-💡 헤더에 마우스를 올리면 이 설명이 보입니다.</t>
-      </text>
-    </comment>
-    <comment ref="E1" authorId="0" shapeId="0">
-      <text>
-        <t>sprite=이미지 한 장(현행) / parts_anim=파츠 애니(추후 전환용 — 단골 표정과 같은 규칙)
-💡 헤더에 마우스를 올리면 이 설명이 보입니다.</t>
-      </text>
-    </comment>
-    <comment ref="F1" authorId="0" shapeId="0">
-      <text>
-        <t>sprite 모드의 리소스 키. 아트 제작 중이라 지금은 가칭 — 완성 시 실키로 교체
-💡 헤더에 마우스를 올리면 이 설명이 보입니다.</t>
-      </text>
-    </comment>
-    <comment ref="G1" authorId="0" shapeId="0">
-      <text>
-        <t>표정별 교체 스프라이트 — '표정:키; 표정:키' (예: joy:Guest/eyes_m_1_joy; anger:…). 표정이 정해지면 이 맵에 있는 표정만 교체, 없으면 기본 sprite 유지. 비우면 표정 고정(현행). 표정은 common 세트, default 등록 금지. 감정 눈 아트가 나오면 eyes 행에 채운다
-💡 헤더에 마우스를 올리면 이 설명이 보입니다.</t>
-      </text>
-    </comment>
-    <comment ref="H1" authorId="0" shapeId="0">
-      <text>
-        <t>추첨 가중치(1 이상 정수). 클수록 자주 나온다
-💡 헤더에 마우스를 올리면 이 설명이 보입니다.</t>
-      </text>
-    </comment>
-    <comment ref="I1" authorId="0" shapeId="0">
-      <text>
-        <t>제작중/OK — 에셋 검수용, 게임 미사용
-💡 헤더에 마우스를 올리면 이 설명이 보입니다.</t>
-      </text>
-    </comment>
-    <comment ref="J1" authorId="0" shapeId="0">
-      <text>
-        <t>기획 메모 (게임 미사용)
 💡 헤더에 마우스를 올리면 이 설명이 보입니다.</t>
       </text>
     </comment>
@@ -1391,6 +1452,89 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00ED7D31"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>grade</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>revenue_mult</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>excellent</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>decent</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>sewage</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:B6"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
     <tabColor rgb="004472C4"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -2032,7 +2176,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V18"/>
+  <dimension ref="A1:Z18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -2052,11 +2196,15 @@
     <col width="21" customWidth="1" min="15" max="15"/>
     <col width="13" customWidth="1" min="16" max="16"/>
     <col width="15" customWidth="1" min="17" max="17"/>
-    <col width="10" customWidth="1" min="18" max="18"/>
-    <col width="13" customWidth="1" min="19" max="19"/>
-    <col width="16" customWidth="1" min="20" max="20"/>
-    <col width="19" customWidth="1" min="21" max="21"/>
+    <col width="60" customWidth="1" min="18" max="18"/>
+    <col width="60" customWidth="1" min="19" max="19"/>
+    <col width="10" customWidth="1" min="20" max="20"/>
+    <col width="13" customWidth="1" min="21" max="21"/>
     <col width="16" customWidth="1" min="22" max="22"/>
+    <col width="19" customWidth="1" min="23" max="23"/>
+    <col width="16" customWidth="1" min="24" max="24"/>
+    <col width="25" customWidth="1" min="25" max="25"/>
+    <col width="22" customWidth="1" min="26" max="26"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2145,29 +2293,49 @@
           <t>tier_override</t>
         </is>
       </c>
-      <c r="R1" s="5" t="inlineStr">
+      <c r="R1" s="4" t="inlineStr">
+        <is>
+          <t>recipe_desc_ko</t>
+        </is>
+      </c>
+      <c r="S1" s="4" t="inlineStr">
+        <is>
+          <t>recipe_desc_en</t>
+        </is>
+      </c>
+      <c r="T1" s="5" t="inlineStr">
         <is>
           <t>(파생)tier</t>
         </is>
       </c>
-      <c r="S1" s="5" t="inlineStr">
+      <c r="U1" s="5" t="inlineStr">
         <is>
           <t>(파생)gimmick</t>
         </is>
       </c>
-      <c r="T1" s="5" t="inlineStr">
+      <c r="V1" s="5" t="inlineStr">
         <is>
           <t>(파생)unlock_day</t>
         </is>
       </c>
-      <c r="U1" s="5" t="inlineStr">
+      <c r="W1" s="5" t="inlineStr">
         <is>
           <t>(파생)scoring_items</t>
         </is>
       </c>
-      <c r="V1" s="5" t="inlineStr">
+      <c r="X1" s="5" t="inlineStr">
         <is>
           <t>(파생)time_limit</t>
+        </is>
+      </c>
+      <c r="Y1" s="5" t="inlineStr">
+        <is>
+          <t>(파생)sprite</t>
+        </is>
+      </c>
+      <c r="Z1" s="5" t="inlineStr">
+        <is>
+          <t>(파생)serve_sprite</t>
         </is>
       </c>
     </row>
@@ -2237,22 +2405,42 @@
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr">
+      <c r="R2" s="6" t="inlineStr">
+        <is>
+          <t>하이볼 잔에 진 1.5oz를 붓고, 토닉워터로 잔을 채워 가볍게 젓는다. 라임 웨지를 걸친다.</t>
+        </is>
+      </c>
+      <c r="S2" s="6" t="inlineStr">
+        <is>
+          <t>Pour 1.5oz gin into a highball glass, top with tonic water, and stir gently. Garnish with a lime wedge.</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
         <is>
           <t>T1</t>
         </is>
       </c>
-      <c r="S2" t="n">
+      <c r="U2" t="n">
         <v>2</v>
       </c>
-      <c r="T2" t="n">
+      <c r="V2" t="n">
         <v>1</v>
       </c>
-      <c r="U2" t="n">
+      <c r="W2" t="n">
         <v>6</v>
       </c>
-      <c r="V2" t="n">
+      <c r="X2" t="n">
         <v>36</v>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Finished_GinTonic</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>Serve_GinTonic</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -2321,22 +2509,42 @@
       <c r="O3" s="7" t="inlineStr"/>
       <c r="P3" s="7" t="inlineStr"/>
       <c r="Q3" s="7" t="inlineStr"/>
-      <c r="R3" s="7" t="inlineStr">
+      <c r="R3" s="8" t="inlineStr">
+        <is>
+          <t>진 1.5oz, 레몬 반 개의 즙, 설탕 1tsp을 셰이킹해 하이볼 잔에 따른다. 소다수로 채우고 레몬 슬라이스를 올린다.</t>
+        </is>
+      </c>
+      <c r="S3" s="8" t="inlineStr">
+        <is>
+          <t>Shake 1.5oz gin, the juice of half a lemon, and 1 tsp sugar, then strain into a highball glass. Top with soda water and add a lemon slice.</t>
+        </is>
+      </c>
+      <c r="T3" s="7" t="inlineStr">
         <is>
           <t>T3</t>
         </is>
       </c>
-      <c r="S3" s="7" t="n">
+      <c r="U3" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="T3" s="7" t="n">
+      <c r="V3" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="U3" s="7" t="n">
+      <c r="W3" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="V3" s="7" t="n">
+      <c r="X3" s="7" t="n">
         <v>52</v>
+      </c>
+      <c r="Y3" s="7" t="inlineStr">
+        <is>
+          <t>Finished_GinFizz</t>
+        </is>
+      </c>
+      <c r="Z3" s="7" t="inlineStr">
+        <is>
+          <t>Serve_GinFizz</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -2401,22 +2609,42 @@
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
       <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr">
+      <c r="R4" s="6" t="inlineStr">
+        <is>
+          <t>오프너로 뚜껑을 딴 뒤 맥주잔에 12oz를 천천히 따른다. 거품이 잔 위로 넘치지 않게 기울여서.</t>
+        </is>
+      </c>
+      <c r="S4" s="6" t="inlineStr">
+        <is>
+          <t>Pop the cap with an opener and pour 12oz slowly into a beer mug, tilted so the head doesn't spill over.</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
         <is>
           <t>T1</t>
         </is>
       </c>
-      <c r="S4" t="n">
+      <c r="U4" t="n">
         <v>2</v>
       </c>
-      <c r="T4" t="n">
+      <c r="V4" t="n">
         <v>1</v>
       </c>
-      <c r="U4" t="n">
+      <c r="W4" t="n">
         <v>5</v>
       </c>
-      <c r="V4" t="n">
+      <c r="X4" t="n">
         <v>36</v>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Finished_BottleBeer</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>Serve_BottleBeer</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -2481,22 +2709,42 @@
       <c r="O5" s="7" t="inlineStr"/>
       <c r="P5" s="7" t="inlineStr"/>
       <c r="Q5" s="7" t="inlineStr"/>
-      <c r="R5" s="7" t="inlineStr">
+      <c r="R5" s="8" t="inlineStr">
+        <is>
+          <t>코르크를 조심스럽게 뽑고 와인잔에 8oz를 따른다. 잔을 흔들지 않는다.</t>
+        </is>
+      </c>
+      <c r="S5" s="8" t="inlineStr">
+        <is>
+          <t>Draw the cork carefully and pour 8oz into a wine glass. Do not swirl.</t>
+        </is>
+      </c>
+      <c r="T5" s="7" t="inlineStr">
         <is>
           <t>T1</t>
         </is>
       </c>
-      <c r="S5" s="7" t="n">
+      <c r="U5" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="T5" s="7" t="n">
+      <c r="V5" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="U5" s="7" t="n">
+      <c r="W5" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="V5" s="7" t="n">
+      <c r="X5" s="7" t="n">
         <v>36</v>
+      </c>
+      <c r="Y5" s="7" t="inlineStr">
+        <is>
+          <t>Finished_RedWine</t>
+        </is>
+      </c>
+      <c r="Z5" s="7" t="inlineStr">
+        <is>
+          <t>Serve_RedWine</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -2561,22 +2809,42 @@
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
       <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr">
+      <c r="R6" s="6" t="inlineStr">
+        <is>
+          <t>코르크를 소리 없이 뽑고 플루트 잔에 8oz를 따른다. 기포가 가라앉기 전에 낸다.</t>
+        </is>
+      </c>
+      <c r="S6" s="6" t="inlineStr">
+        <is>
+          <t>Ease the cork out without a pop and pour 8oz into a flute. Serve before the bubbles settle.</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
         <is>
           <t>T1</t>
         </is>
       </c>
-      <c r="S6" t="n">
+      <c r="U6" t="n">
         <v>2</v>
       </c>
-      <c r="T6" t="n">
+      <c r="V6" t="n">
         <v>1</v>
       </c>
-      <c r="U6" t="n">
+      <c r="W6" t="n">
         <v>5</v>
       </c>
-      <c r="V6" t="n">
+      <c r="X6" t="n">
         <v>36</v>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Finished_Champagne</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>Serve_Champagne</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -2637,22 +2905,42 @@
       <c r="O7" s="7" t="inlineStr"/>
       <c r="P7" s="7" t="inlineStr"/>
       <c r="Q7" s="7" t="inlineStr"/>
-      <c r="R7" s="7" t="inlineStr">
+      <c r="R7" s="8" t="inlineStr">
+        <is>
+          <t>하이볼 잔에 보드카 1.5oz와 오렌지주스 6oz를 넣고 젓는다.</t>
+        </is>
+      </c>
+      <c r="S7" s="8" t="inlineStr">
+        <is>
+          <t>Build 1.5oz vodka and 6oz orange juice in a highball glass and stir.</t>
+        </is>
+      </c>
+      <c r="T7" s="7" t="inlineStr">
         <is>
           <t>T2</t>
         </is>
       </c>
-      <c r="S7" s="7" t="n">
+      <c r="U7" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="T7" s="7" t="n">
+      <c r="V7" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="U7" s="7" t="n">
+      <c r="W7" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="V7" s="7" t="n">
+      <c r="X7" s="7" t="n">
         <v>44</v>
+      </c>
+      <c r="Y7" s="7" t="inlineStr">
+        <is>
+          <t>Finished_Screwdriver</t>
+        </is>
+      </c>
+      <c r="Z7" s="7" t="inlineStr">
+        <is>
+          <t>Serve_Screwdriver</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -2721,22 +3009,42 @@
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
       <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr">
+      <c r="R8" s="6" t="inlineStr">
+        <is>
+          <t>맥주잔에 보드카 1.5oz와 라임 반 개의 즙을 넣고 젓는다. 진저에일로 채우고 라임 웨지를 걸친다.</t>
+        </is>
+      </c>
+      <c r="S8" s="6" t="inlineStr">
+        <is>
+          <t>Build 1.5oz vodka and the juice of half a lime in a mug and stir. Top with ginger ale and garnish with a lime wedge.</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
         <is>
           <t>T2</t>
         </is>
       </c>
-      <c r="S8" t="n">
+      <c r="U8" t="n">
         <v>3</v>
       </c>
-      <c r="T8" t="n">
+      <c r="V8" t="n">
         <v>3</v>
       </c>
-      <c r="U8" t="n">
+      <c r="W8" t="n">
         <v>7</v>
       </c>
-      <c r="V8" t="n">
+      <c r="X8" t="n">
         <v>44</v>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>Finished_MoscowMule</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>Serve_MoscowMule</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -2801,22 +3109,42 @@
       <c r="O9" s="7" t="inlineStr"/>
       <c r="P9" s="7" t="inlineStr"/>
       <c r="Q9" s="7" t="inlineStr"/>
-      <c r="R9" s="7" t="inlineStr">
+      <c r="R9" s="8" t="inlineStr">
+        <is>
+          <t>콜린스 잔에 데킬라 1oz와 오렌지주스 6oz를 넣고 젓는다. 오렌지 슬라이스를 올린다.</t>
+        </is>
+      </c>
+      <c r="S9" s="8" t="inlineStr">
+        <is>
+          <t>Build 1oz tequila and 6oz orange juice in a collins glass and stir. Garnish with an orange slice.</t>
+        </is>
+      </c>
+      <c r="T9" s="7" t="inlineStr">
         <is>
           <t>T2</t>
         </is>
       </c>
-      <c r="S9" s="7" t="n">
+      <c r="U9" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="T9" s="7" t="n">
+      <c r="V9" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="U9" s="7" t="n">
+      <c r="W9" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="V9" s="7" t="n">
+      <c r="X9" s="7" t="n">
         <v>44</v>
+      </c>
+      <c r="Y9" s="7" t="inlineStr">
+        <is>
+          <t>Finished_TequilaSunrise</t>
+        </is>
+      </c>
+      <c r="Z9" s="7" t="inlineStr">
+        <is>
+          <t>Serve_TequilaSunrise</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -2885,22 +3213,42 @@
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
       <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="inlineStr">
+      <c r="R10" s="6" t="inlineStr">
+        <is>
+          <t>콜린스 잔에 진·보드카·럼·데킬라를 1oz씩 넣고 라임 반 개의 즙을 더해 젓는다. 콜라로 채우고 레몬 슬라이스를 올린다.</t>
+        </is>
+      </c>
+      <c r="S10" s="6" t="inlineStr">
+        <is>
+          <t>Build 1oz each of gin, vodka, rum, and tequila in a collins glass, add the juice of half a lime, and stir. Top with cola and add a lemon slice.</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
         <is>
           <t>T5</t>
         </is>
       </c>
-      <c r="S10" t="n">
+      <c r="U10" t="n">
         <v>6</v>
       </c>
-      <c r="T10" t="n">
+      <c r="V10" t="n">
         <v>3</v>
       </c>
-      <c r="U10" t="n">
+      <c r="W10" t="n">
         <v>10</v>
       </c>
-      <c r="V10" t="n">
+      <c r="X10" t="n">
         <v>68</v>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Finished_LongIsland</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>Serve_LongIsland</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -2969,22 +3317,42 @@
       <c r="O11" s="7" t="inlineStr"/>
       <c r="P11" s="7" t="inlineStr"/>
       <c r="Q11" s="7" t="inlineStr"/>
-      <c r="R11" s="7" t="inlineStr">
+      <c r="R11" s="8" t="inlineStr">
+        <is>
+          <t>위스키 1.5oz, 레몬 반 개의 즙, 설탕 1tsp을 셰이킹해 온더락 잔에 따른다. 사워믹스로 채우고 체리를 올린다.</t>
+        </is>
+      </c>
+      <c r="S11" s="8" t="inlineStr">
+        <is>
+          <t>Shake 1.5oz whiskey, the juice of half a lemon, and 1 tsp sugar, then strain into a rocks glass. Top with sour mix and garnish with a cherry.</t>
+        </is>
+      </c>
+      <c r="T11" s="7" t="inlineStr">
         <is>
           <t>T3</t>
         </is>
       </c>
-      <c r="S11" s="7" t="n">
+      <c r="U11" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="T11" s="7" t="n">
+      <c r="V11" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="U11" s="7" t="n">
+      <c r="W11" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="V11" s="7" t="n">
+      <c r="X11" s="7" t="n">
         <v>52</v>
+      </c>
+      <c r="Y11" s="7" t="inlineStr">
+        <is>
+          <t>Finished_WhiskeySour</t>
+        </is>
+      </c>
+      <c r="Z11" s="7" t="inlineStr">
+        <is>
+          <t>Serve_WhiskeySour</t>
+        </is>
       </c>
     </row>
     <row r="12">
@@ -3049,22 +3417,42 @@
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr"/>
       <c r="Q12" t="inlineStr"/>
-      <c r="R12" t="inlineStr">
+      <c r="R12" s="6" t="inlineStr">
+        <is>
+          <t>믹싱 글라스에 진 6oz와 드라이 버무스 1.5oz를 넣고 스터한 뒤 칵테일 잔에 따른다. 올리브를 넣는다.</t>
+        </is>
+      </c>
+      <c r="S12" s="6" t="inlineStr">
+        <is>
+          <t>Stir 6oz gin with 1.5oz dry vermouth in a mixing glass, then strain into a cocktail glass. Drop in an olive.</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
         <is>
           <t>T2</t>
         </is>
       </c>
-      <c r="S12" t="n">
+      <c r="U12" t="n">
         <v>3</v>
       </c>
-      <c r="T12" t="n">
+      <c r="V12" t="n">
         <v>1</v>
       </c>
-      <c r="U12" t="n">
+      <c r="W12" t="n">
         <v>6</v>
       </c>
-      <c r="V12" t="n">
+      <c r="X12" t="n">
         <v>44</v>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Finished_DryMartini</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>Serve_DryMartini</t>
+        </is>
       </c>
     </row>
     <row r="13">
@@ -3125,22 +3513,42 @@
       <c r="O13" s="7" t="inlineStr"/>
       <c r="P13" s="7" t="inlineStr"/>
       <c r="Q13" s="7" t="inlineStr"/>
-      <c r="R13" s="7" t="inlineStr">
+      <c r="R13" s="8" t="inlineStr">
+        <is>
+          <t>럼 4.5oz, 그레나딘 0.75oz, 라임즙 1.5oz를 셰이킹해 칵테일 잔에 따른다.</t>
+        </is>
+      </c>
+      <c r="S13" s="8" t="inlineStr">
+        <is>
+          <t>Shake 4.5oz rum, 0.75oz grenadine, and 1.5oz lime juice, then strain into a cocktail glass.</t>
+        </is>
+      </c>
+      <c r="T13" s="7" t="inlineStr">
         <is>
           <t>T3</t>
         </is>
       </c>
-      <c r="S13" s="7" t="n">
+      <c r="U13" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="T13" s="7" t="n">
+      <c r="V13" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="U13" s="7" t="n">
+      <c r="W13" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="V13" s="7" t="n">
+      <c r="X13" s="7" t="n">
         <v>52</v>
+      </c>
+      <c r="Y13" s="7" t="inlineStr">
+        <is>
+          <t>Finished_Bacardi</t>
+        </is>
+      </c>
+      <c r="Z13" s="7" t="inlineStr">
+        <is>
+          <t>Serve_Bacardi</t>
+        </is>
       </c>
     </row>
     <row r="14">
@@ -3205,22 +3613,42 @@
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr"/>
       <c r="Q14" t="inlineStr"/>
-      <c r="R14" t="inlineStr">
+      <c r="R14" s="6" t="inlineStr">
+        <is>
+          <t>보드카 4oz, 쿠앵트로 1.5oz, 크랜베리주스 3oz, 라임즙 1.5oz를 셰이킹해 칵테일 잔에 따른다. 레몬 슬라이스를 올린다.</t>
+        </is>
+      </c>
+      <c r="S14" s="6" t="inlineStr">
+        <is>
+          <t>Shake 4oz vodka, 1.5oz cointreau, 3oz cranberry juice, and 1.5oz lime juice, then strain into a cocktail glass. Add a lemon slice.</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
         <is>
           <t>T4</t>
         </is>
       </c>
-      <c r="S14" t="n">
+      <c r="U14" t="n">
         <v>5</v>
       </c>
-      <c r="T14" t="n">
+      <c r="V14" t="n">
         <v>2</v>
       </c>
-      <c r="U14" t="n">
+      <c r="W14" t="n">
         <v>8</v>
       </c>
-      <c r="V14" t="n">
+      <c r="X14" t="n">
         <v>60</v>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>Finished_Cosmopolitan</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>Serve_Cosmopolitan</t>
+        </is>
       </c>
     </row>
     <row r="15">
@@ -3285,22 +3713,42 @@
       <c r="O15" s="7" t="inlineStr"/>
       <c r="P15" s="7" t="inlineStr"/>
       <c r="Q15" s="7" t="inlineStr"/>
-      <c r="R15" s="7" t="inlineStr">
+      <c r="R15" s="8" t="inlineStr">
+        <is>
+          <t>데킬라 3.5oz, 트리플섹 2oz, 레몬즙 1.5oz를 셰이킹해 칵테일 잔에 따른다. 라임 웨지를 걸친다.</t>
+        </is>
+      </c>
+      <c r="S15" s="8" t="inlineStr">
+        <is>
+          <t>Shake 3.5oz tequila, 2oz triple sec, and 1.5oz lemon juice, then strain into a cocktail glass. Garnish with a lime wedge.</t>
+        </is>
+      </c>
+      <c r="T15" s="7" t="inlineStr">
         <is>
           <t>T3</t>
         </is>
       </c>
-      <c r="S15" s="7" t="n">
+      <c r="U15" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="T15" s="7" t="n">
+      <c r="V15" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="U15" s="7" t="n">
+      <c r="W15" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="V15" s="7" t="n">
+      <c r="X15" s="7" t="n">
         <v>52</v>
+      </c>
+      <c r="Y15" s="7" t="inlineStr">
+        <is>
+          <t>Finished_Margarita</t>
+        </is>
+      </c>
+      <c r="Z15" s="7" t="inlineStr">
+        <is>
+          <t>Serve_Margarita</t>
+        </is>
       </c>
     </row>
     <row r="16">
@@ -3361,22 +3809,42 @@
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr"/>
       <c r="Q16" t="inlineStr"/>
-      <c r="R16" t="inlineStr">
+      <c r="R16" s="6" t="inlineStr">
+        <is>
+          <t>진 40ml, 트리플섹 30ml, 레몬즙 20ml를 셰이킹해 칵테일 잔에 따른다.</t>
+        </is>
+      </c>
+      <c r="S16" s="6" t="inlineStr">
+        <is>
+          <t>Shake 40ml gin, 30ml triple sec, and 20ml lemon juice, then strain into a cocktail glass.</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
         <is>
           <t>T3</t>
         </is>
       </c>
-      <c r="S16" t="n">
+      <c r="U16" t="n">
         <v>4</v>
       </c>
-      <c r="T16" t="n">
+      <c r="V16" t="n">
         <v>6</v>
       </c>
-      <c r="U16" t="n">
+      <c r="W16" t="n">
         <v>7</v>
       </c>
-      <c r="V16" t="n">
+      <c r="X16" t="n">
         <v>52</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>Finished_WhiteLady</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>Serve_WhiteLady</t>
+        </is>
       </c>
     </row>
     <row r="17">
@@ -3437,22 +3905,42 @@
       <c r="O17" s="7" t="inlineStr"/>
       <c r="P17" s="7" t="inlineStr"/>
       <c r="Q17" s="7" t="inlineStr"/>
-      <c r="R17" s="7" t="inlineStr">
+      <c r="R17" s="8" t="inlineStr">
+        <is>
+          <t>온더락 잔에 칼루아 1.5oz를 붓고 우유 0.75oz를 위에 얹듯 천천히 따른다.</t>
+        </is>
+      </c>
+      <c r="S17" s="8" t="inlineStr">
+        <is>
+          <t>Pour 1.5oz kahlua into a rocks glass, then layer 0.75oz milk slowly on top.</t>
+        </is>
+      </c>
+      <c r="T17" s="7" t="inlineStr">
         <is>
           <t>T2</t>
         </is>
       </c>
-      <c r="S17" s="7" t="n">
+      <c r="U17" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="T17" s="7" t="n">
+      <c r="V17" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="U17" s="7" t="n">
+      <c r="W17" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="V17" s="7" t="n">
+      <c r="X17" s="7" t="n">
         <v>44</v>
+      </c>
+      <c r="Y17" s="7" t="inlineStr">
+        <is>
+          <t>Finished_KahluaMilk</t>
+        </is>
+      </c>
+      <c r="Z17" s="7" t="inlineStr">
+        <is>
+          <t>Serve_KahluaMilk</t>
+        </is>
       </c>
     </row>
     <row r="18">
@@ -3517,32 +4005,301 @@
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr"/>
       <c r="Q18" t="inlineStr"/>
-      <c r="R18" t="inlineStr">
+      <c r="R18" s="6" t="inlineStr">
+        <is>
+          <t>진 2oz, 벌꿀 원액 0.75oz, 레몬즙 0.75oz를 셰이킹해 칵테일 잔에 따른다. 레몬 슬라이스를 올린다.</t>
+        </is>
+      </c>
+      <c r="S18" s="6" t="inlineStr">
+        <is>
+          <t>Shake 2oz gin, 0.75oz honey syrup, and 0.75oz lemon juice, then strain into a cocktail glass. Add a lemon slice.</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
         <is>
           <t>T3</t>
         </is>
       </c>
-      <c r="S18" t="n">
+      <c r="U18" t="n">
         <v>4</v>
       </c>
-      <c r="T18" t="n">
+      <c r="V18" t="n">
         <v>99</v>
       </c>
-      <c r="U18" t="n">
+      <c r="W18" t="n">
         <v>7</v>
       </c>
-      <c r="V18" t="n">
+      <c r="X18" t="n">
         <v>52</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>Finished_BeesKnees</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>Serve_BeesKnees</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:V18"/>
+  <autoFilter ref="A1:Z18"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="004472C4"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>tag_ko</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>tag_en</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>가벼운</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Light</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>저도수·부담 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>달콤한</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>Sweet</t>
+        </is>
+      </c>
+      <c r="C3" s="7" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>독한</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>고도수</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>묵직한</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>Heavy</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>바디감</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>부드러운</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Smooth</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>비밀</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>Secret</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>비밀 레시피 계열</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>상큼한</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Fresh</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>시트러스</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>새콤한</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>Tangy</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>씁쓸한</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Bitter</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>알싸한</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>Spicy</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>진저 계열의 톡 쏘는 맛</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>우아한</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Elegant</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>청량한</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>Crisp</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>탄산감</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>클래식</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Classic</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>화사한</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>Bright</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:C15"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="004472C4"/>
@@ -4747,7 +5504,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="004472C4"/>
@@ -6710,7 +7467,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="004472C4"/>
@@ -6928,7 +7685,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="0070AD47"/>
@@ -7180,14 +7937,14 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00ED7D31"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D35"/>
+  <dimension ref="A1:D36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
@@ -7855,148 +8612,87 @@
     <row r="33">
       <c r="A33" s="7" t="inlineStr">
         <is>
-          <t>order_bark_gap_sec</t>
-        </is>
-      </c>
-      <c r="B33" s="7" t="n">
-        <v>1.5</v>
+          <t>sfx_serve</t>
+        </is>
+      </c>
+      <c r="B33" s="7" t="inlineStr">
+        <is>
+          <t>SFX_glass_slide</t>
+        </is>
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>str</t>
         </is>
       </c>
       <c r="D33" s="8" t="inlineStr">
         <is>
-          <t>주문 대사 사이의 텀 — ask_order→order_think→order 순서로 재생할 때, 앞 대사 타이핑이 끝나고 다음 대사까지 기다리는 초 [가안]</t>
+          <t>제공 컷씬 공용 사운드(잔 미는 소리) — 구엔진 이식, 전 칵테일 공용</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>street_typing_interval_ms</t>
+          <t>order_bark_gap_sec</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>50</v>
+        <v>1.5</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>float</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>거리 말풍선 타이핑 문자당 간격(ms) — 바(typing_interval_ms)와 별도 튜닝</t>
+          <t>주문 대사 사이의 텀 — ask_order→order_think→order 순서로 재생할 때, 앞 대사 타이핑이 끝나고 다음 대사까지 기다리는 초 [가안]</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="7" t="inlineStr">
         <is>
+          <t>street_typing_interval_ms</t>
+        </is>
+      </c>
+      <c r="B35" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="C35" s="7" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="D35" s="8" t="inlineStr">
+        <is>
+          <t>거리 말풍선 타이핑 문자당 간격(ms) — 바(typing_interval_ms)와 별도 튜닝</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
           <t>street_auto_next_delay_sec</t>
         </is>
       </c>
-      <c r="B35" s="7" t="n">
+      <c r="B36" t="n">
         <v>3</v>
       </c>
-      <c r="C35" s="7" t="inlineStr">
+      <c r="C36" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="D35" s="8" t="inlineStr">
+      <c r="D36" s="6" t="inlineStr">
         <is>
           <t>auto 재생 대사 — 타이핑 종료 후 다음 대사까지 텀</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D35"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="00ED7D31"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="11" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>grade</t>
-        </is>
-      </c>
-      <c r="B1" s="4" t="inlineStr">
-        <is>
-          <t>min_pct</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>excellent</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="7" t="inlineStr">
-        <is>
-          <t>good</t>
-        </is>
-      </c>
-      <c r="B3" s="7" t="n">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>decent</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>poor</t>
-        </is>
-      </c>
-      <c r="B5" s="7" t="n">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>sewage</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:B6"/>
+  <autoFilter ref="A1:D36"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
@@ -8013,7 +8709,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8024,7 +8720,7 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>revenue_mult</t>
+          <t>min_pct</t>
         </is>
       </c>
     </row>
@@ -8035,7 +8731,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.2</v>
+        <v>95</v>
       </c>
     </row>
     <row r="3">
@@ -8045,7 +8741,7 @@
         </is>
       </c>
       <c r="B3" s="7" t="n">
-        <v>1</v>
+        <v>80</v>
       </c>
     </row>
     <row r="4">
@@ -8055,7 +8751,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7</v>
+        <v>60</v>
       </c>
     </row>
     <row r="5">
@@ -8065,7 +8761,7 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>0.3</v>
+        <v>35</v>
       </c>
     </row>
     <row r="6">
@@ -8075,7 +8771,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Document/데이터/LUNA_System.xlsx
+++ b/Document/데이터/LUNA_System.xlsx
@@ -1622,7 +1622,6 @@
           <t>m</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>sprite</t>
@@ -1633,7 +1632,6 @@
           <t>Guest/body_m</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
         <v>1</v>
       </c>
@@ -1706,7 +1704,6 @@
           <t>m</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
           <t>sprite</t>
@@ -1717,7 +1714,6 @@
           <t>Guest/eyes_m_1</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
         <v>1</v>
       </c>
@@ -1782,7 +1778,6 @@
           <t>f</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
           <t>sprite</t>
@@ -1793,7 +1788,6 @@
           <t>Guest/eyes_f_1</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
         <v>1</v>
       </c>
@@ -1858,7 +1852,6 @@
           <t>m</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
           <t>sprite</t>
@@ -1869,7 +1862,6 @@
           <t>Guest/hair_m_1</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
         <v>1</v>
       </c>
@@ -1934,7 +1926,6 @@
           <t>f</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
           <t>sprite</t>
@@ -1945,7 +1936,6 @@
           <t>Guest/hair_f_1</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
         <v>1</v>
       </c>
@@ -2010,7 +2000,6 @@
           <t>m</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
           <t>sprite</t>
@@ -2021,7 +2010,6 @@
           <t>Guest/outfit_m_1</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
         <v>1</v>
       </c>
@@ -2094,7 +2082,6 @@
           <t>f</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
           <t>sprite</t>
@@ -2105,7 +2092,6 @@
           <t>Guest/outfit_f_1</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
         <v>1</v>
       </c>
@@ -2371,7 +2357,6 @@
           <t>build</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
           <t>tonic_water</t>
@@ -2402,9 +2387,6 @@
           <t>Gin and tonic. The simplest, and therefore the most honest.</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
       <c r="R2" s="6" t="inlineStr">
         <is>
           <t>하이볼 잔에 진 1.5oz를 붓고, 토닉워터로 잔을 채워 가볍게 젓는다. 라임 웨지를 걸친다.</t>
@@ -2584,8 +2566,6 @@
           <t>cap</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
           <t>202,162,4</t>
@@ -2606,9 +2586,6 @@
           <t>The pop of the cap is the appetizer. Served with a glass.</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
       <c r="R4" s="6" t="inlineStr">
         <is>
           <t>오프너로 뚜껑을 딴 뒤 맥주잔에 12oz를 천천히 따른다. 거품이 잔 위로 넘치지 않게 기울여서.</t>
@@ -2784,8 +2761,6 @@
           <t>cork</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
           <t>255,245,225</t>
@@ -2806,9 +2781,6 @@
           <t>While the bubbles rise, everyone's the main character.</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
       <c r="R6" s="6" t="inlineStr">
         <is>
           <t>코르크를 소리 없이 뽑고 플루트 잔에 8oz를 따른다. 기포가 가라앉기 전에 낸다.</t>
@@ -2975,7 +2947,6 @@
           <t>build</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
           <t>ginger_ale</t>
@@ -3006,9 +2977,6 @@
           <t>The ginger kick they say feels like a mule's hind leg.</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
       <c r="R8" s="6" t="inlineStr">
         <is>
           <t>맥주잔에 보드카 1.5oz와 라임 반 개의 즙을 넣고 젓는다. 진저에일로 채우고 라임 웨지를 걸친다.</t>
@@ -3179,7 +3147,6 @@
           <t>build</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
           <t>cola</t>
@@ -3210,9 +3177,6 @@
           <t>Not a drop of tea in it. That's the trap.</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr"/>
       <c r="R10" s="6" t="inlineStr">
         <is>
           <t>콜린스 잔에 진·보드카·럼·데킬라를 1oz씩 넣고 라임 반 개의 즙을 더해 젓는다. 콜라로 채우고 레몬 슬라이스를 올린다.</t>
@@ -3387,8 +3351,6 @@
           <t>stir</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
           <t>olive</t>
@@ -3414,9 +3376,6 @@
           <t>Beware the customer who says 'shaken, not stirred.'</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr"/>
       <c r="R12" s="6" t="inlineStr">
         <is>
           <t>믹싱 글라스에 진 6oz와 드라이 버무스 1.5oz를 넣고 스터한 뒤 칵테일 잔에 따른다. 올리브를 넣는다.</t>
@@ -3583,8 +3542,6 @@
           <t>shake</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
           <t>lemon_slice</t>
@@ -3610,9 +3567,6 @@
           <t>Urban red. Trends pass; the taste stays.</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr"/>
       <c r="R14" s="6" t="inlineStr">
         <is>
           <t>보드카 4oz, 쿠앵트로 1.5oz, 크랜베리주스 3oz, 라임즙 1.5oz를 셰이킹해 칵테일 잔에 따른다. 레몬 슬라이스를 올린다.</t>
@@ -3783,9 +3737,6 @@
           <t>shake</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
           <t>247,241,214</t>
@@ -3806,9 +3757,6 @@
           <t>Elegant as a white dress. The proof is not elegant.</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr"/>
-      <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="inlineStr"/>
       <c r="R16" s="6" t="inlineStr">
         <is>
           <t>진 40ml, 트리플섹 30ml, 레몬즙 20ml를 셰이킹해 칵테일 잔에 따른다.</t>
@@ -3975,8 +3923,6 @@
           <t>shake</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
           <t>lemon_slice</t>
@@ -4002,9 +3948,6 @@
           <t>A Prohibition-era bootleg cocktail — real honey to mask cheap gin. Slang for 'the best.'</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr"/>
-      <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr"/>
       <c r="R18" s="6" t="inlineStr">
         <is>
           <t>진 2oz, 벌꿀 원액 0.75oz, 레몬즙 0.75oz를 셰이킹해 칵테일 잔에 따른다. 레몬 슬라이스를 올린다.</t>
@@ -4157,7 +4100,6 @@
           <t>Smooth</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
@@ -4217,7 +4159,6 @@
           <t>Bitter</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
@@ -4247,7 +4188,6 @@
           <t>Elegant</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
@@ -4277,7 +4217,6 @@
           <t>Classic</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
@@ -5621,12 +5560,9 @@
           <t>230,235,240</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
         <v>1</v>
       </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
           <t>주니퍼베리 향의 증류주. 칵테일의 기본기.</t>
@@ -5717,12 +5653,9 @@
           <t>98,15,11</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
         <v>1</v>
       </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
           <t>잔에 따르는 순간부터 분위기가 달라진다.</t>
@@ -5813,12 +5746,9 @@
           <t>245,250,255</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
         <v>1</v>
       </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
           <t>씁쓸한 탄산. 진의 가장 오랜 친구.</t>
@@ -5904,12 +5834,9 @@
           <t>fruit</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
         <v>1</v>
       </c>
-      <c r="I8" t="inlineStr"/>
       <c r="J8" t="n">
         <v>20</v>
       </c>
@@ -6001,12 +5928,9 @@
           <t>240,235,220</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
         <v>3</v>
       </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
           <t>아가베의 태양을 병에 담은 것.</t>
@@ -6097,12 +6021,9 @@
           <t>180,120,60</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
         <v>3</v>
       </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
           <t>사탕수수와 항해의 술.</t>
@@ -6195,11 +6116,9 @@
           <t>230,200,120</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
         <v>3</v>
       </c>
-      <c r="I14" t="inlineStr"/>
       <c r="J14" t="n">
         <v>25</v>
       </c>
@@ -6290,12 +6209,9 @@
           <t>fruit</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
         <v>2</v>
       </c>
-      <c r="I16" t="inlineStr"/>
       <c r="J16" t="n">
         <v>20</v>
       </c>
@@ -6389,12 +6305,9 @@
           <t>220,220,190</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
       <c r="H18" t="n">
         <v>1</v>
       </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
           <t>마티니를 마티니로 만드는 한 방울.</t>
@@ -6485,11 +6398,9 @@
           <t>230,220,160</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
         <v>4</v>
       </c>
-      <c r="I20" t="inlineStr"/>
       <c r="J20" t="n">
         <v>25</v>
       </c>
@@ -6583,11 +6494,9 @@
           <t>170,30,60</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
       <c r="H22" t="n">
         <v>2</v>
       </c>
-      <c r="I22" t="inlineStr"/>
       <c r="J22" t="n">
         <v>25</v>
       </c>
@@ -6681,12 +6590,9 @@
           <t>60,35,25</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
       <c r="H24" t="n">
         <v>2</v>
       </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
           <t>커피를 술로 번역한 것.</t>
@@ -6779,7 +6685,6 @@
           <t>235,180,60</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr"/>
       <c r="H26" t="n">
         <v>99</v>
       </c>
@@ -6788,7 +6693,6 @@
           <t>flag.q_samho_honey_done</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
           <t>삼호의 창고에서 나온 진짜 꿀. 요즘 세상엔 금값이다.</t>
@@ -6865,8 +6769,6 @@
           <t>Wine Glass</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
           <t>glass_wine</t>
@@ -6875,8 +6777,6 @@
       <c r="H28" t="n">
         <v>1</v>
       </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr">
         <is>
           <t>다리가 긴 잔. 향을 가둔다.</t>
@@ -6953,8 +6853,6 @@
           <t>Highball Glass</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
           <t>glass_highball</t>
@@ -6963,8 +6861,6 @@
       <c r="H30" t="n">
         <v>1</v>
       </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr">
         <is>
           <t>탄산 롱드링크의 표준.</t>
@@ -7041,8 +6937,6 @@
           <t>Rocks Glass</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
           <t>glass_rocks</t>
@@ -7051,8 +6945,6 @@
       <c r="H32" t="n">
         <v>1</v>
       </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr">
         <is>
           <t>낮고 두꺼운 잔. 얼음과 독주의 자리.</t>
@@ -7129,8 +7021,6 @@
           <t>Shaker</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
           <t>tool_shaker</t>
@@ -7139,8 +7029,6 @@
       <c r="H34" t="n">
         <v>1</v>
       </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
         <is>
           <t>셰이킹 기믹용.</t>
@@ -7217,8 +7105,6 @@
           <t>Opener</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
           <t>tool_opener</t>
@@ -7227,8 +7113,6 @@
       <c r="H36" t="n">
         <v>1</v>
       </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr">
         <is>
           <t>병뚜껑도 코르크도 이걸로 — 병따기·코르크 따기 기믹용.</t>
@@ -7305,8 +7189,6 @@
           <t>Lemon Slice</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
           <t>gn_lemon</t>
@@ -7315,8 +7197,6 @@
       <c r="H38" t="n">
         <v>1</v>
       </c>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr">
         <is>
           <t>레몬 슬라이스 장식.</t>
@@ -7393,8 +7273,6 @@
           <t>Cherry</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
           <t>gn_cherry</t>
@@ -7403,8 +7281,6 @@
       <c r="H40" t="n">
         <v>1</v>
       </c>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr">
         <is>
           <t>사워 칵테일의 마침표.</t>
@@ -7944,7 +7820,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D36"/>
+  <dimension ref="A1:D38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
@@ -8688,6 +8564,46 @@
       <c r="D36" s="6" t="inlineStr">
         <is>
           <t>auto 재생 대사 — 타이핑 종료 후 다음 대사까지 텀</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>stir_stacks</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>10</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>스터 게이지 스택 수(결과 칸) — 전 칵테일 공통, 성공·실패 불문 시도 하나가 한 칸을 채운다 [가안]</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>stir_stack_sec</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>2</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>스터 시도(스택 한 칸) 제한시간(초) — 초과 시 실패 스택 [가안]</t>
         </is>
       </c>
     </row>

--- a/Document/데이터/LUNA_System.xlsx
+++ b/Document/데이터/LUNA_System.xlsx
@@ -18,6 +18,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GradeCuts" sheetId="9" state="visible" r:id="rId9"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GradePayout" sheetId="10" state="visible" r:id="rId10"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GuestBodies" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GuestBodyExclusions" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Cocktails'!$A$1:$Z$18</definedName>
@@ -452,6 +453,36 @@
       <text>
         <t>기획 메모 (게임 미사용)
 💡 헤더에 마우스를 올리면 이 설명이 보입니다.</t>
+      </text>
+    </comment>
+    <comment ref="K1" authorId="0" shapeId="0">
+      <text>
+        <t>TRUE = 그 성별·슬롯의 기본 파츠. 성별×필수 슬롯마다 정확히 1개, personalities 공란 필수. 리소스 로드 실패 시 이 조합으로 대체(선택 슬롯은 항상 미착용)</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment11.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>LUNA 데이터 가이드</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0" shapeId="0">
+      <text>
+        <t>금지 쌍의 한쪽 파츠 id (GuestBodies.id)</t>
+      </text>
+    </comment>
+    <comment ref="B1" authorId="0" shapeId="0">
+      <text>
+        <t>금지 쌍의 다른쪽 파츠 id — (a,b)와 (b,a)는 같은 규칙, 한 행만 등록</t>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="0" shapeId="0">
+      <text>
+        <t>금지 이유 — 검수용, json 미배포 (예: 민소매 아님)</t>
       </text>
     </comment>
   </commentList>
@@ -1539,7 +1570,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J15"/>
+  <dimension ref="A1:K33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1605,6 +1636,11 @@
           <t>note</t>
         </is>
       </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>is_default</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1637,13 +1673,16 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>제작중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="J2" s="6" t="inlineStr">
         <is>
-          <t>남성 바디 — 얼굴·몸통·코·입·패널 라인을 붙여 한 장으로 제작</t>
-        </is>
+          <t>실물 body.png — 얼굴·몸통·코·패널 라인 한 장</t>
+        </is>
+      </c>
+      <c r="K2" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -1687,6 +1726,9 @@
           <t>여성 바디 — 얼굴·몸통·코·입·패널 라인을 붙여 한 장으로 제작</t>
         </is>
       </c>
+      <c r="K3" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1719,10 +1761,17 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>제작중</t>
-        </is>
-      </c>
-      <c r="J4" s="6" t="inlineStr"/>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="J4" s="6" t="inlineStr">
+        <is>
+          <t>실물 Eye_1</t>
+        </is>
+      </c>
+      <c r="K4" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
@@ -1757,10 +1806,14 @@
       </c>
       <c r="I5" s="7" t="inlineStr">
         <is>
-          <t>제작중</t>
-        </is>
-      </c>
-      <c r="J5" s="8" t="inlineStr"/>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="J5" s="8" t="inlineStr">
+        <is>
+          <t>실물 Eye_2</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1797,6 +1850,9 @@
         </is>
       </c>
       <c r="J6" s="6" t="inlineStr"/>
+      <c r="K6" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
@@ -1867,10 +1923,17 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>제작중</t>
-        </is>
-      </c>
-      <c r="J8" s="6" t="inlineStr"/>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="J8" s="6" t="inlineStr">
+        <is>
+          <t>실물 Hair_1</t>
+        </is>
+      </c>
+      <c r="K8" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
@@ -1905,10 +1968,14 @@
       </c>
       <c r="I9" s="7" t="inlineStr">
         <is>
-          <t>제작중</t>
-        </is>
-      </c>
-      <c r="J9" s="8" t="inlineStr"/>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="J9" s="8" t="inlineStr">
+        <is>
+          <t>실물 Hair_2</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1945,6 +2012,9 @@
         </is>
       </c>
       <c r="J10" s="6" t="inlineStr"/>
+      <c r="K10" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
@@ -2015,13 +2085,16 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>제작중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="J12" s="6" t="inlineStr">
         <is>
-          <t>민소매</t>
-        </is>
+          <t>실물 Shirt_1 — 프린트 티(반소매)</t>
+        </is>
+      </c>
+      <c r="K12" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -2057,12 +2130,12 @@
       </c>
       <c r="I13" s="7" t="inlineStr">
         <is>
-          <t>제작중</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="J13" s="8" t="inlineStr">
         <is>
-          <t>아우터</t>
+          <t>실물 Shirt_1(2) — 색 변형</t>
         </is>
       </c>
     </row>
@@ -2105,6 +2178,9 @@
           <t>민소매</t>
         </is>
       </c>
+      <c r="K14" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
@@ -2148,8 +2224,879 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>outfit</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>outfit_m_3</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Guest/outfit_m_3</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>1</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>실물 Shirt_1(3) — 색 변형</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>outfit</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>outfit_m_4</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Guest/outfit_m_4</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>실물 Shirt_1(4) — 색 변형</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>outfit</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>outfit_m_5</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Guest/outfit_m_5</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>실물 Shirt_1(5) — 색 변형</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>outfit</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>outfit_m_6</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Guest/outfit_m_6</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>1</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>실물 Shirt_2 — 소매 있음</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>outfit</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>outfit_m_7</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Guest/outfit_m_7</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>1</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>실물 Shirt_3 — 민소매(팔 액세서리 허용)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>outfit</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>outfit_m_8</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Guest/outfit_m_8</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>실물 Shirt_3(2) — 민소매 색 변형(팔 액세서리 허용)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>outerwear</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>outerwear_m_1</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Guest/outerwear_m_1</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
+        <v>1</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>실물 Acc_2 — 어깨 재킷</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>necklace</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>necklace_m_1</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Guest/necklace_m_1</t>
+        </is>
+      </c>
+      <c r="H23" t="n">
+        <v>1</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>실물 Acc_3 — 목걸이</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>eyes</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>eyes_m_3</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Guest/eyes_m_3</t>
+        </is>
+      </c>
+      <c r="H24" t="n">
+        <v>1</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>실물 Eye_3</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>eyebrows</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>eyebrows_m_1</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Guest/eyebrows_m_1</t>
+        </is>
+      </c>
+      <c r="H25" t="n">
+        <v>1</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>실물 Eyebrow_1</t>
+        </is>
+      </c>
+      <c r="K25" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>eyebrows</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>eyebrows_m_2</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Guest/eyebrows_m_2</t>
+        </is>
+      </c>
+      <c r="H26" t="n">
+        <v>1</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>실물 Eyebrow_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>eyebrows</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>eyebrows_m_3</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Guest/eyebrows_m_3</t>
+        </is>
+      </c>
+      <c r="H27" t="n">
+        <v>1</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>실물 Eyebrow_3</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>eyebrows</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>eyebrows_f_1</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Guest/eyebrows_f_1</t>
+        </is>
+      </c>
+      <c r="H28" t="n">
+        <v>1</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>신규필요</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>여성 눈썹 — 아트 대기</t>
+        </is>
+      </c>
+      <c r="K28" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>mouth</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>mouth_m_1</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Guest/mouth_m_1</t>
+        </is>
+      </c>
+      <c r="H29" t="n">
+        <v>1</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>실물 mouth_1</t>
+        </is>
+      </c>
+      <c r="K29" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>mouth</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>mouth_m_2</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Guest/mouth_m_2</t>
+        </is>
+      </c>
+      <c r="H30" t="n">
+        <v>1</v>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>실물 mouth_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>mouth</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>mouth_m_3</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Guest/mouth_m_3</t>
+        </is>
+      </c>
+      <c r="H31" t="n">
+        <v>1</v>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>실물 mouth_3</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>mouth</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>mouth_f_1</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Guest/mouth_f_1</t>
+        </is>
+      </c>
+      <c r="H32" t="n">
+        <v>1</v>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>신규필요</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>여성 입 — 아트 대기</t>
+        </is>
+      </c>
+      <c r="K32" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>arm_accessory</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>arm_accessory_m_1</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Guest/arm_accessory_m_1</t>
+        </is>
+      </c>
+      <c r="H33" t="n">
+        <v>1</v>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>실물 Acc_1 — 팔 액세서리, 민소매 전용(GuestBodyExclusions 참조)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:J15"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="44" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>part_a</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>part_b</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>arm_accessory_m_1</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>outfit_m_1</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>민소매 아님 — 소매가 팔 액세서리를 가린다</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>arm_accessory_m_1</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>outfit_m_2</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>민소매 아님</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>arm_accessory_m_1</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>outfit_m_3</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>민소매 아님</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>arm_accessory_m_1</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>outfit_m_4</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>민소매 아님</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>arm_accessory_m_1</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>outfit_m_5</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>민소매 아님</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>arm_accessory_m_1</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>outfit_m_6</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>민소매 아님</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
@@ -7820,7 +8767,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D38"/>
+  <dimension ref="A1:D39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
@@ -8604,6 +9551,26 @@
       <c r="D38" t="inlineStr">
         <is>
           <t>스터 시도(스택 한 칸) 제한시간(초) — 초과 시 실패 스택 [가안]</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>guest_acc_none_weight</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>1</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>랜덤 손님 선택 슬롯(아우터·목걸이·팔 액세서리)의 '없음' 후보 가중치 — 클수록 미착용이 흔하다. 없음 1·파츠 합 3이면 미착용 25% [가안]</t>
         </is>
       </c>
     </row>

--- a/Document/데이터/LUNA_System.xlsx
+++ b/Document/데이터/LUNA_System.xlsx
@@ -2,19 +2,19 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="INFO" sheetId="1" r:id="R843a5047c8ec47a3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cocktails" sheetId="2" r:id="R6ed637563fd94174"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tags" sheetId="3" r:id="R4548bef31c904227"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RecipeLines" sheetId="4" r:id="R6a8518ce40ce40f0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ShelfItems" sheetId="5" r:id="R3213268dedbf4418"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Personalities" sheetId="6" r:id="Rbefe44248ed94206"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RandomWaves" sheetId="7" r:id="Rfe9015831d6744cc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Config" sheetId="8" r:id="Rd59f045f629c4095"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GradeCuts" sheetId="9" r:id="R848dcae68f8b4a42"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SettlementRules" sheetId="10" r:id="R7330104cad294116"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ScoreBands" sheetId="11" r:id="R867af5951b9c4873"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GuestBodies" sheetId="12" r:id="Rb081a8392e634f33"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GuestBodyExclusions" sheetId="13" r:id="Rf4d25c1f090f4a8c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="INFO" sheetId="1" r:id="R54ca5335968e41dd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cocktails" sheetId="2" r:id="Rf8c7200bd6ee4156"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tags" sheetId="3" r:id="Re3bbe7dfd2d04794"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RecipeLines" sheetId="4" r:id="R898cd14a21d74d18"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ShelfItems" sheetId="5" r:id="R4c79fbfede6a4bef"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Personalities" sheetId="6" r:id="R4e0ba96c3f314739"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RandomWaves" sheetId="7" r:id="R61e2d244fc394577"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Config" sheetId="8" r:id="Rfd0c3d3023694cf3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GradeCuts" sheetId="9" r:id="R515099ba95724683"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SettlementRules" sheetId="10" r:id="Rf385daf2b51c4d4d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ScoreBands" sheetId="11" r:id="R4feee996f4a34f8d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GuestBodies" sheetId="12" r:id="Rd3f58f7ff5c34f9b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GuestBodyExclusions" sheetId="13" r:id="R988003b2da9f4acc"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -977,6 +977,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:numFmts count="1">
+    <x:numFmt numFmtId="200" formatCode="0.00"/>
+  </x:numFmts>
   <x:fonts count="5">
     <x:font>
       <x:sz val="11"/>
@@ -1063,7 +1066,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="16">
+  <x:cellXfs count="17">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1104,6 +1107,7 @@
     <x:xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="4" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="200" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -1952,7 +1956,7 @@
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1aaaa5ff40164b5f"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd33f2fe6c42e468f"/>
 </x:worksheet>
 </file>
 
@@ -2325,7 +2329,7 @@
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4c38137630644ac2"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re018786ff5384c18"/>
 </x:worksheet>
 </file>
 
@@ -4168,7 +4172,7 @@
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R50f148f3698545a9"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9b37baefe1524bdb"/>
 </x:worksheet>
 </file>
 
@@ -4305,7 +4309,7 @@
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8232423aa7d04f25"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3b91248fcaf5434a"/>
 </x:worksheet>
 </file>
 
@@ -7760,7 +7764,7 @@
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R569cfb87b6ca4ba5"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rad3f179ddbc9426b"/>
 </x:worksheet>
 </file>
 
@@ -8173,7 +8177,7 @@
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra4f3c470632f421f"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0bba3893827e4835"/>
 </x:worksheet>
 </file>
 
@@ -11891,7 +11895,7 @@
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R64f995a312bd4507"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc614eb9449a64d2b"/>
 </x:worksheet>
 </file>
 
@@ -11919,6 +11923,7 @@
     <x:col min="15" max="15" width="20" customWidth="1"/>
     <x:col min="16" max="16" width="21" customWidth="1"/>
     <x:col min="17" max="17" width="14" hidden="0" customWidth="1"/>
+    <x:col min="18" max="18" width="14" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
@@ -11973,6 +11978,9 @@
       <x:c r="Q1" t="str">
         <x:v>shelf_group</x:v>
       </x:c>
+      <x:c r="R1" t="str">
+        <x:v>liquid_alpha</x:v>
+      </x:c>
     </x:row>
     <x:row r="2">
       <x:c r="A2" t="str">
@@ -12018,6 +12026,9 @@
       <x:c r="Q2" t="str">
         <x:v>liquor</x:v>
       </x:c>
+      <x:c r="R2" s="16" t="n">
+        <x:v>0.35</x:v>
+      </x:c>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="7" t="str">
@@ -12065,6 +12076,9 @@
       <x:c r="Q3" t="str">
         <x:v>fridge</x:v>
       </x:c>
+      <x:c r="R3" s="16" t="n">
+        <x:v>0.75</x:v>
+      </x:c>
     </x:row>
     <x:row r="4">
       <x:c r="A4" t="str">
@@ -12110,6 +12124,9 @@
       <x:c r="Q4" t="str">
         <x:v>liquor</x:v>
       </x:c>
+      <x:c r="R4" s="16" t="n">
+        <x:v>0.75</x:v>
+      </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="7" t="str">
@@ -12155,6 +12172,9 @@
       <x:c r="Q5" t="str">
         <x:v>liquor</x:v>
       </x:c>
+      <x:c r="R5" s="16" t="n">
+        <x:v>0.35</x:v>
+      </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" t="str">
@@ -12200,6 +12220,9 @@
       <x:c r="Q6" t="str">
         <x:v>fridge</x:v>
       </x:c>
+      <x:c r="R6" s="16" t="n">
+        <x:v>0.35</x:v>
+      </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="7" t="str">
@@ -12243,6 +12266,7 @@
         <x:v>tsp</x:v>
       </x:c>
       <x:c r="Q7"/>
+      <x:c r="R7" s="16"/>
     </x:row>
     <x:row r="8">
       <x:c r="A8" t="str">
@@ -12286,6 +12310,7 @@
         <x:v>oz</x:v>
       </x:c>
       <x:c r="Q8"/>
+      <x:c r="R8" s="16"/>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="7" t="str">
@@ -12331,6 +12356,9 @@
       <x:c r="Q9" t="str">
         <x:v>liquor</x:v>
       </x:c>
+      <x:c r="R9" s="16" t="n">
+        <x:v>0.35</x:v>
+      </x:c>
     </x:row>
     <x:row r="10">
       <x:c r="A10" t="str">
@@ -12376,6 +12404,9 @@
       <x:c r="Q10" t="str">
         <x:v>liquor</x:v>
       </x:c>
+      <x:c r="R10" s="16" t="n">
+        <x:v>0.35</x:v>
+      </x:c>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="7" t="str">
@@ -12421,6 +12452,9 @@
       <x:c r="Q11" t="str">
         <x:v>liquor</x:v>
       </x:c>
+      <x:c r="R11" s="16" t="n">
+        <x:v>0.75</x:v>
+      </x:c>
     </x:row>
     <x:row r="12">
       <x:c r="A12" t="str">
@@ -12468,6 +12502,9 @@
       <x:c r="Q12" t="str">
         <x:v>fridge</x:v>
       </x:c>
+      <x:c r="R12" s="16" t="n">
+        <x:v>0.75</x:v>
+      </x:c>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="7" t="str">
@@ -12515,6 +12552,9 @@
       <x:c r="Q13" t="str">
         <x:v>fridge</x:v>
       </x:c>
+      <x:c r="R13" s="16" t="n">
+        <x:v>0.75</x:v>
+      </x:c>
     </x:row>
     <x:row r="14">
       <x:c r="A14" t="str">
@@ -12561,6 +12601,9 @@
       </x:c>
       <x:c r="Q14" t="str">
         <x:v>fridge</x:v>
+      </x:c>
+      <x:c r="R14" s="16" t="n">
+        <x:v>0.75</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
@@ -12605,6 +12648,7 @@
         <x:v>oz</x:v>
       </x:c>
       <x:c r="Q15"/>
+      <x:c r="R15" s="16"/>
     </x:row>
     <x:row r="16">
       <x:c r="A16" t="str">
@@ -12650,6 +12694,9 @@
       <x:c r="Q16" t="str">
         <x:v>liquor</x:v>
       </x:c>
+      <x:c r="R16" s="16" t="n">
+        <x:v>0.75</x:v>
+      </x:c>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="7" t="str">
@@ -12695,6 +12742,9 @@
       <x:c r="Q17" t="str">
         <x:v>liquor</x:v>
       </x:c>
+      <x:c r="R17" s="16" t="n">
+        <x:v>0.35</x:v>
+      </x:c>
     </x:row>
     <x:row r="18">
       <x:c r="A18" t="str">
@@ -12740,6 +12790,9 @@
       <x:c r="Q18" t="str">
         <x:v>liquor</x:v>
       </x:c>
+      <x:c r="R18" s="16" t="n">
+        <x:v>0.75</x:v>
+      </x:c>
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="7" t="str">
@@ -12786,6 +12839,9 @@
       </x:c>
       <x:c r="Q19" t="str">
         <x:v>fridge</x:v>
+      </x:c>
+      <x:c r="R19" s="16" t="n">
+        <x:v>0.75</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
@@ -12832,6 +12888,9 @@
       <x:c r="Q20" t="str">
         <x:v>liquor</x:v>
       </x:c>
+      <x:c r="R20" s="16" t="n">
+        <x:v>0.35</x:v>
+      </x:c>
     </x:row>
     <x:row r="21">
       <x:c r="A21" s="7" t="str">
@@ -12878,6 +12937,9 @@
       </x:c>
       <x:c r="Q21" t="str">
         <x:v>fridge</x:v>
+      </x:c>
+      <x:c r="R21" s="16" t="n">
+        <x:v>0.75</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
@@ -12924,6 +12986,9 @@
       <x:c r="Q22" t="str">
         <x:v>liquor</x:v>
       </x:c>
+      <x:c r="R22" s="16" t="n">
+        <x:v>0.35</x:v>
+      </x:c>
     </x:row>
     <x:row r="23">
       <x:c r="A23" s="7" t="str">
@@ -12969,6 +13034,9 @@
       <x:c r="Q23" t="str">
         <x:v>liquor</x:v>
       </x:c>
+      <x:c r="R23" s="16" t="n">
+        <x:v>0.75</x:v>
+      </x:c>
     </x:row>
     <x:row r="24">
       <x:c r="A24" t="str">
@@ -13015,6 +13083,9 @@
       </x:c>
       <x:c r="Q24" t="str">
         <x:v>fridge</x:v>
+      </x:c>
+      <x:c r="R24" s="16" t="n">
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
@@ -13061,6 +13132,9 @@
       <x:c r="Q25" t="str">
         <x:v>liquor</x:v>
       </x:c>
+      <x:c r="R25" s="16" t="n">
+        <x:v>0.75</x:v>
+      </x:c>
     </x:row>
     <x:row r="26">
       <x:c r="A26" t="str">
@@ -13106,6 +13180,9 @@
       <x:c r="Q26" t="str">
         <x:v>liquor</x:v>
       </x:c>
+      <x:c r="R26" s="16" t="n">
+        <x:v>0.75</x:v>
+      </x:c>
     </x:row>
     <x:row r="27">
       <x:c r="A27" s="7" t="str">
@@ -13152,6 +13229,9 @@
       </x:c>
       <x:c r="Q27" t="str">
         <x:v>fridge</x:v>
+      </x:c>
+      <x:c r="R27" s="16" t="n">
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="28">
@@ -13198,6 +13278,9 @@
       <x:c r="Q28" t="str">
         <x:v>liquor</x:v>
       </x:c>
+      <x:c r="R28" s="16" t="n">
+        <x:v>0.75</x:v>
+      </x:c>
     </x:row>
     <x:row r="29">
       <x:c r="A29" s="7" t="str">
@@ -13243,6 +13326,9 @@
       <x:c r="Q29" t="str">
         <x:v>liquor</x:v>
       </x:c>
+      <x:c r="R29" s="16" t="n">
+        <x:v>0.35</x:v>
+      </x:c>
     </x:row>
     <x:row r="30">
       <x:c r="A30" t="str">
@@ -13289,6 +13375,9 @@
       </x:c>
       <x:c r="Q30" t="str">
         <x:v>fridge</x:v>
+      </x:c>
+      <x:c r="R30" s="16" t="n">
+        <x:v>0.75</x:v>
       </x:c>
     </x:row>
     <x:row r="31">
@@ -13335,6 +13424,9 @@
       <x:c r="Q31" t="str">
         <x:v>liquor</x:v>
       </x:c>
+      <x:c r="R31" s="16" t="n">
+        <x:v>0.75</x:v>
+      </x:c>
     </x:row>
     <x:row r="32">
       <x:c r="A32" t="str">
@@ -13380,6 +13472,9 @@
       <x:c r="Q32" t="str">
         <x:v>liquor</x:v>
       </x:c>
+      <x:c r="R32" s="16" t="n">
+        <x:v>0.75</x:v>
+      </x:c>
     </x:row>
     <x:row r="33">
       <x:c r="A33" s="7" t="str">
@@ -13427,6 +13522,9 @@
       <x:c r="Q33" t="str">
         <x:v>fridge</x:v>
       </x:c>
+      <x:c r="R33" s="16" t="n">
+        <x:v>0.75</x:v>
+      </x:c>
     </x:row>
     <x:row r="34">
       <x:c r="A34" t="str">
@@ -13473,6 +13571,9 @@
       </x:c>
       <x:c r="Q34" t="str">
         <x:v>fridge</x:v>
+      </x:c>
+      <x:c r="R34" s="16" t="n">
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="35">
@@ -13519,6 +13620,9 @@
       <x:c r="Q35" t="str">
         <x:v>liquor</x:v>
       </x:c>
+      <x:c r="R35" s="16" t="n">
+        <x:v>0.75</x:v>
+      </x:c>
     </x:row>
     <x:row r="36">
       <x:c r="A36" t="str">
@@ -13564,6 +13668,9 @@
       <x:c r="Q36" t="str">
         <x:v>liquor</x:v>
       </x:c>
+      <x:c r="R36" s="16" t="n">
+        <x:v>0.75</x:v>
+      </x:c>
     </x:row>
     <x:row r="37">
       <x:c r="A37" s="7" t="str">
@@ -13609,6 +13716,9 @@
       <x:c r="Q37" t="str">
         <x:v>liquor</x:v>
       </x:c>
+      <x:c r="R37" s="16" t="n">
+        <x:v>0.35</x:v>
+      </x:c>
     </x:row>
     <x:row r="38">
       <x:c r="A38" t="str">
@@ -13653,6 +13763,9 @@
       </x:c>
       <x:c r="Q38" t="str">
         <x:v>liquor</x:v>
+      </x:c>
+      <x:c r="R38" s="16" t="n">
+        <x:v>0.75</x:v>
       </x:c>
     </x:row>
     <x:row r="39">
@@ -13689,6 +13802,7 @@
       <x:c r="O39" s="7"/>
       <x:c r="P39" s="7"/>
       <x:c r="Q39"/>
+      <x:c r="R39" s="16"/>
     </x:row>
     <x:row r="40">
       <x:c r="A40" t="str">
@@ -13724,6 +13838,7 @@
       <x:c r="O40"/>
       <x:c r="P40"/>
       <x:c r="Q40"/>
+      <x:c r="R40" s="16"/>
     </x:row>
     <x:row r="41">
       <x:c r="A41" s="7" t="str">
@@ -13759,6 +13874,7 @@
       <x:c r="O41" s="7"/>
       <x:c r="P41" s="7"/>
       <x:c r="Q41"/>
+      <x:c r="R41" s="16"/>
     </x:row>
     <x:row r="42">
       <x:c r="A42" t="str">
@@ -13794,6 +13910,7 @@
       <x:c r="O42"/>
       <x:c r="P42"/>
       <x:c r="Q42"/>
+      <x:c r="R42" s="16"/>
     </x:row>
     <x:row r="43">
       <x:c r="A43" s="7" t="str">
@@ -13829,6 +13946,7 @@
       <x:c r="O43" s="7"/>
       <x:c r="P43" s="7"/>
       <x:c r="Q43"/>
+      <x:c r="R43" s="16"/>
     </x:row>
     <x:row r="44">
       <x:c r="A44" t="str">
@@ -13864,6 +13982,7 @@
       <x:c r="O44"/>
       <x:c r="P44"/>
       <x:c r="Q44"/>
+      <x:c r="R44" s="16"/>
     </x:row>
     <x:row r="45">
       <x:c r="A45" s="7" t="str">
@@ -13899,6 +14018,7 @@
       <x:c r="O45" s="7"/>
       <x:c r="P45" s="7"/>
       <x:c r="Q45"/>
+      <x:c r="R45" s="16"/>
     </x:row>
     <x:row r="46">
       <x:c r="A46" t="str">
@@ -13934,6 +14054,7 @@
       <x:c r="O46"/>
       <x:c r="P46"/>
       <x:c r="Q46"/>
+      <x:c r="R46" s="16"/>
     </x:row>
     <x:row r="47">
       <x:c r="A47" s="7" t="str">
@@ -13969,6 +14090,7 @@
       <x:c r="O47" s="7"/>
       <x:c r="P47" s="7"/>
       <x:c r="Q47"/>
+      <x:c r="R47" s="16"/>
     </x:row>
     <x:row r="48">
       <x:c r="A48" t="str">
@@ -14004,6 +14126,7 @@
       <x:c r="O48"/>
       <x:c r="P48"/>
       <x:c r="Q48"/>
+      <x:c r="R48" s="16"/>
     </x:row>
     <x:row r="49">
       <x:c r="A49" s="7" t="str">
@@ -14039,6 +14162,7 @@
       <x:c r="O49" s="7"/>
       <x:c r="P49" s="7"/>
       <x:c r="Q49"/>
+      <x:c r="R49" s="16"/>
     </x:row>
     <x:row r="50">
       <x:c r="A50" t="str">
@@ -14074,6 +14198,7 @@
       <x:c r="O50"/>
       <x:c r="P50"/>
       <x:c r="Q50"/>
+      <x:c r="R50" s="16"/>
     </x:row>
     <x:row r="51">
       <x:c r="A51" s="7" t="str">
@@ -14109,6 +14234,7 @@
       <x:c r="O51" s="7"/>
       <x:c r="P51" s="7"/>
       <x:c r="Q51"/>
+      <x:c r="R51" s="16"/>
     </x:row>
     <x:row r="52">
       <x:c r="A52"/>
@@ -14130,8 +14256,14 @@
       <x:c r="Q52"/>
     </x:row>
   </x:sheetData>
+  <x:dataValidations count="1">
+    <x:dataValidation type="decimal" operator="between" sqref="R2:R51">
+      <x:formula1>0</x:formula1>
+      <x:formula2>1</x:formula2>
+    </x:dataValidation>
+  </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd2cb3bb59a9740c9"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0422a7bdfbed4af1"/>
 </x:worksheet>
 </file>
 
@@ -14345,7 +14477,7 @@
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0298d865ea124375"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc63f5c7a9558438b"/>
 </x:worksheet>
 </file>
 
@@ -14665,7 +14797,7 @@
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9529311c5d5f41ef"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R57f065009cf14a14"/>
 </x:worksheet>
 </file>
 
@@ -16028,7 +16160,7 @@
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbf172fa9c6da4e64"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5dd51dd4633e4f2f"/>
 </x:worksheet>
 </file>
 
@@ -16107,6 +16239,6 @@
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re147b1b03be2401e"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R209e17c962c04540"/>
 </x:worksheet>
 </file>